--- a/clients/1_Test/Test_assessment_results.xlsx
+++ b/clients/1_Test/Test_assessment_results.xlsx
@@ -4809,9 +4809,9 @@
   </sheetData>
   <mergeCells count="221">
     <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D60:D63"/>
     <mergeCell ref="D53:D55"/>
     <mergeCell ref="E39:E40"/>
-    <mergeCell ref="D60:D63"/>
     <mergeCell ref="F60:F63"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="G48:G49"/>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="E5" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="E119" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="D4" s="78" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>test</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="D6" s="78" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>test</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="D8" s="78" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>test</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D10" s="78" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>test</t>
         </is>
       </c>
     </row>

--- a/clients/1_Test/Test_assessment_results.xlsx
+++ b/clients/1_Test/Test_assessment_results.xlsx
@@ -2000,7 +2000,7 @@
       <c r="D7" s="18" t="n"/>
       <c r="E7" s="18" t="n"/>
       <c r="F7" s="21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" s="22" t="n"/>
     </row>
@@ -2273,7 +2273,7 @@
       <c r="E23" s="18" t="n"/>
       <c r="F23" s="18" t="n"/>
       <c r="G23" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C30" s="18" t="n"/>
       <c r="D30" s="19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E30" s="18" t="n"/>
       <c r="F30" s="18" t="n"/>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D39" s="18" t="n"/>
       <c r="E39" s="18" t="n"/>
@@ -2698,7 +2698,7 @@
       <c r="E48" s="18" t="n"/>
       <c r="F48" s="18" t="n"/>
       <c r="G48" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
